--- a/src/main/resources/client-labels/apc-etiquetas-retail.xlsx
+++ b/src/main/resources/client-labels/apc-etiquetas-retail.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jordi\Documents\Workspace\Packing List Automation\docs\Etiquetas cajas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\target\muestras-etiquetas-apc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06D092B-CF91-481F-A82D-44C8C4C3681A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9494D4-BA46-4D6F-9E85-72262A211C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11928" yWindow="552" windowWidth="17280" windowHeight="8964" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etiquette colis Retail" sheetId="1" r:id="rId1"/>
     <sheet name="Etiquette Palette Retail" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Etiquette colis Retail'!$A$1:$D$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Etiquette Palette Retail'!$A$1:$D$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
   <si>
     <r>
       <t xml:space="preserve">DESTINATAIRE
@@ -114,38 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pieces by size : </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nombre total de colis sur la palette
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial Black"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Total number of packages on the palette)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Poids brut 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial Black"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Total gross weight)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -203,22 +175,114 @@
     <t xml:space="preserve">, </t>
   </si>
   <si>
-    <t>PXCBS-F67066</t>
-  </si>
-  <si>
-    <t>PUN20260717WH1</t>
-  </si>
-  <si>
     <t>LZZ-NOIR</t>
   </si>
   <si>
-    <t>89 / 89</t>
-  </si>
-  <si>
-    <t>3,00 kg</t>
-  </si>
-  <si>
     <t>RETAIL</t>
+  </si>
+  <si>
+    <t>EXPEDITEUR
+(Shipper / Sender)
+-
+PROVENANCE
+(Origin)</t>
+  </si>
+  <si>
+    <t>DESTINATAIRE
+(Consignee)</t>
+  </si>
+  <si>
+    <t>DESTINATION
+(Destination)</t>
+  </si>
+  <si>
+    <t>4100128863</t>
+  </si>
+  <si>
+    <t>PUN20260928WH1</t>
+  </si>
+  <si>
+    <t>PXCBC-F67008</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1 / 3</t>
+  </si>
+  <si>
+    <t>7,60 Kg</t>
+  </si>
+  <si>
+    <t>Nombre total de colis sur la palette
+(Total number of packages on the palette)</t>
+  </si>
+  <si>
+    <t>Poids brut 
+(Total gross weight)</t>
+  </si>
+  <si>
+    <t>25,20 Kg</t>
+  </si>
+  <si>
+    <t>16,20 Kg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nombre total de colis sur la palette
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Total number of packages on the palette)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Poids brut 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Total gross weight)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EXPEDITEUR
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Shipper / Sender)
+-
+PROVENANCE
+(Origin)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -228,7 +292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,12 +347,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -299,6 +357,19 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -373,10 +444,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -424,8 +495,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -433,9 +505,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -461,15 +535,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:colOff>3227160</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>502957</xdr:colOff>
+      <xdr:colOff>856742</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>94901</xdr:rowOff>
+      <xdr:rowOff>96715</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -499,8 +573,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3175000" y="158750"/>
-          <a:ext cx="1874557" cy="602901"/>
+          <a:off x="3485696" y="215900"/>
+          <a:ext cx="1684510" cy="668215"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -522,9 +596,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>3131910</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1677707" cy="672751"/>
     <xdr:pic>
@@ -555,7 +629,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3159125" y="158750"/>
+          <a:off x="3390446" y="8681358"/>
           <a:ext cx="1677707" cy="672751"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -583,15 +657,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2746375</xdr:colOff>
+      <xdr:colOff>2079624</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>601382</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>47276</xdr:rowOff>
+      <xdr:colOff>782356</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>94901</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -621,8 +695,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3048000" y="142875"/>
-          <a:ext cx="1868207" cy="606076"/>
+          <a:off x="2256517" y="156483"/>
+          <a:ext cx="1696303" cy="666401"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -641,13 +715,57 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2161268</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>88447</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>864000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>169740</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2338161" y="6524626"/>
+          <a:ext cx="1696303" cy="652793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -685,9 +803,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -720,26 +838,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -772,26 +873,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -965,317 +1049,286 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="11" customWidth="1"/>
-    <col min="2" max="3" width="60.6640625" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="11.5546875" style="11"/>
+    <col min="1" max="1" customWidth="true" style="11" width="3.85546875"/>
+    <col min="2" max="3" customWidth="true" style="11" width="60.7109375"/>
+    <col min="4" max="4" customWidth="true" style="11" width="3.85546875"/>
+    <col min="5" max="16384" style="11" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="2.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B6" s="16" t="s">
+    <row r="1" spans="1:3" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="90.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:3" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="2:3" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="21" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="90.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
+      <c r="C26" s="17"/>
+    </row>
+    <row r="27" spans="2:3" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="59.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="3" t="s">
+      <c r="C29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="32.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
+      <c r="C30" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="5">
-        <v>4100128725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="2:3" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="10"/>
+    </row>
+    <row r="38" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="12"/>
+    </row>
+    <row r="39" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="10"/>
-    </row>
-    <row r="19" spans="2:3" ht="46.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="46.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="17"/>
-    </row>
-    <row r="28" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:3" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" ht="82.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="5">
-        <v>4100128725</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B34" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="25.2" x14ac:dyDescent="0.3">
-      <c r="B36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="10"/>
-    </row>
-    <row r="39" spans="2:3" ht="46.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="46.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="C39" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
   </mergeCells>
-  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0" top="0" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="66" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B4:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="11" customWidth="1"/>
-    <col min="2" max="3" width="57.5546875" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="11.5546875" style="11"/>
+    <col min="1" max="1" customWidth="true" style="11" width="2.5703125"/>
+    <col min="2" max="3" customWidth="true" style="11" width="44.85546875"/>
+    <col min="4" max="4" customWidth="true" style="11" width="2.5703125"/>
+    <col min="5" max="16384" style="11" width="11.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D1" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
+    <row r="4" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:3" ht="98.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:4" ht="109.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="13" t="s">
-        <v>11</v>
+    </row>
+    <row r="8" spans="2:3" ht="93.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="93.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="10"/>
-    </row>
-    <row r="13" spans="2:4" ht="45.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2">
-        <v>55.4</v>
-      </c>
-    </row>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="10"/>
+    </row>
+    <row r="11" spans="2:3" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:3" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
+  <mergeCells count="4">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="84" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>